--- a/danh_sach_thuoc_lieu_dung.xlsx
+++ b/danh_sach_thuoc_lieu_dung.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Backup Sever\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0375826A-C353-4ACF-9CD9-77C602D1A6EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8700443-C341-4FDB-A78B-161812F6152E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15930" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15150" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="115">
   <si>
     <t>Amoxicilin</t>
   </si>
@@ -364,6 +364,18 @@
   </si>
   <si>
     <t>5 mg/kg/ngày;</t>
+  </si>
+  <si>
+    <t>Dạng uống và đặt trực tràng được chỉ định dùng dài ngày trong bệnh thoái hóa khớp, viêm cột sống dính khớp, các bệnh khớp mạn tính khác và viêm khớp lứa tuổi thanh thiếu niên.</t>
+  </si>
+  <si>
+    <t>Không được dùng meloxicam cho những người có triệu chứng hen phế quản, polyp mũi, phù mạch thần kinh hoặc bị phù Quincke, mày đay xuất hiện khi dùng aspirin hoặc các thuốc chống viêm không steroid khác.
+Loét dạ dày - tá tràng tiến triển.
+Chảy máu dạ dày, chảy máu não.
+Điều trị đau sau phẫu thuật bắc cầu nối mạch vành.
+Không dùng dạng thuốc đặt trực tràng cho người có tiền sử viêm trực tràng hoặc chảy máu trực tràng.
+Suy gan nặng và suy thận nặng không lọc máu.
+Phụ nữ có thai và cho con bú.</t>
   </si>
 </sst>
 </file>
@@ -405,10 +417,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -690,7 +705,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.140625" bestFit="1" customWidth="1"/>
@@ -1026,7 +1041,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>76</v>
       </c>
@@ -1037,7 +1052,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>77</v>
       </c>
@@ -1048,7 +1063,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>80</v>
       </c>
@@ -1059,7 +1074,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>88</v>
       </c>
@@ -1067,7 +1082,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>90</v>
       </c>
@@ -1075,7 +1090,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>92</v>
       </c>
@@ -1086,7 +1101,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>94</v>
       </c>
@@ -1097,7 +1112,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>96</v>
       </c>
@@ -1107,8 +1122,14 @@
       <c r="C40" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D40" t="s">
+        <v>113</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>97</v>
       </c>
@@ -1119,7 +1140,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>99</v>
       </c>
